--- a/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
+++ b/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
@@ -886,7 +886,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1082,7 +1082,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
+++ b/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
@@ -887,7 +887,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
@@ -937,12 +937,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">

--- a/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
+++ b/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
@@ -937,7 +937,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">

--- a/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
+++ b/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
@@ -566,14 +566,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -662,6 +662,62 @@
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>mdm.sec.thirteenf.information_table.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.title_of_class</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>share_class</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>class (lines)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.thirteenf.information_table.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>share_classes_filed</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>classes.class_sample (lines)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Matching only</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.thirteenf.information_table.security.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.share_classes_filed</t>
         </is>
       </c>
     </row>
@@ -821,16 +877,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,6 +923,43 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>share_class_one_letter</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>The value matches [A-Z]</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>matching.share_classes_filed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Counted only</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>quality.sec.thirteenf.information_table.security.v1.checks[0]</t>
         </is>
       </c>
     </row>
@@ -881,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -964,25 +1057,57 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>share_class</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
+++ b/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
+++ b/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
@@ -980,7 +980,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">

--- a/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
+++ b/rules/sources/sec.thirteenf.information_table/MAPPING.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical data elements" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data quality" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline targets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1124,6 +1126,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Run checks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lease seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Heartbeat seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
